--- a/artfynd/A 22474-2024 artfynd.xlsx
+++ b/artfynd/A 22474-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119521171</v>
+        <v>119521076</v>
       </c>
       <c r="B2" t="n">
         <v>82305</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>790719</v>
+        <v>790721</v>
       </c>
       <c r="R2" t="n">
-        <v>7287498</v>
+        <v>7287505</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119522576</v>
+        <v>119522491</v>
       </c>
       <c r="B3" t="n">
-        <v>82305</v>
+        <v>57326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,30 +801,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>790642</v>
+        <v>790694</v>
       </c>
       <c r="R3" t="n">
-        <v>7287496</v>
+        <v>7287449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,13 +871,17 @@
           <t>2024-08-27</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119522491</v>
+        <v>119521207</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>82305</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,31 +916,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>790694</v>
+        <v>790725</v>
       </c>
       <c r="R4" t="n">
-        <v>7287449</v>
+        <v>7287490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,17 +985,13 @@
           <t>2024-08-27</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119521207</v>
+        <v>119522475</v>
       </c>
       <c r="B5" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>790725</v>
+        <v>790694</v>
       </c>
       <c r="R5" t="n">
-        <v>7287490</v>
+        <v>7287449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119521228</v>
+        <v>119522629</v>
       </c>
       <c r="B6" t="n">
-        <v>82305</v>
+        <v>103418</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,34 +1132,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>790722</v>
+        <v>790642</v>
       </c>
       <c r="R6" t="n">
-        <v>7287487</v>
+        <v>7287513</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,6 +1200,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>många!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119522475</v>
+        <v>119521228</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>82305</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1248,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>790694</v>
+        <v>790722</v>
       </c>
       <c r="R7" t="n">
-        <v>7287449</v>
+        <v>7287487</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1342,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119521076</v>
+        <v>119522576</v>
       </c>
       <c r="B8" t="n">
         <v>82305</v>
@@ -1387,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>790721</v>
+        <v>790642</v>
       </c>
       <c r="R8" t="n">
-        <v>7287505</v>
+        <v>7287496</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119522629</v>
+        <v>119521171</v>
       </c>
       <c r="B9" t="n">
-        <v>103418</v>
+        <v>82305</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,31 +1464,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1494,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>790642</v>
+        <v>790719</v>
       </c>
       <c r="R9" t="n">
-        <v>7287513</v>
+        <v>7287498</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,11 +1535,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>många!</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22474-2024 artfynd.xlsx
+++ b/artfynd/A 22474-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>119521076</v>
       </c>
       <c r="B2" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119522491</v>
+        <v>119521171</v>
       </c>
       <c r="B3" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,31 +791,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>790694</v>
+        <v>790719</v>
       </c>
       <c r="R3" t="n">
-        <v>7287449</v>
+        <v>7287498</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,17 +860,13 @@
           <t>2024-08-27</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,12 +888,7 @@
         <v>119521207</v>
       </c>
       <c r="B4" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119522475</v>
+        <v>119521228</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>790694</v>
+        <v>790722</v>
       </c>
       <c r="R5" t="n">
-        <v>7287449</v>
+        <v>7287487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,43 +1095,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119522629</v>
+        <v>119522576</v>
       </c>
       <c r="B6" t="n">
-        <v>103418</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,7 +1140,7 @@
         <v>790642</v>
       </c>
       <c r="R6" t="n">
-        <v>7287513</v>
+        <v>7287496</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,11 +1173,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>många!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,46 +1200,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119521228</v>
+        <v>119522491</v>
       </c>
       <c r="B7" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1279,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>790722</v>
+        <v>790694</v>
       </c>
       <c r="R7" t="n">
-        <v>7287487</v>
+        <v>7287449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,13 +1281,17 @@
           <t>2024-08-27</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1342,46 +1310,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119522576</v>
+        <v>119522629</v>
       </c>
       <c r="B8" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,7 +1352,7 @@
         <v>790642</v>
       </c>
       <c r="R8" t="n">
-        <v>7287496</v>
+        <v>7287513</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,6 +1387,11 @@
           <t>2024-08-27</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>många!</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1449,116 +1414,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>119521171</v>
-      </c>
-      <c r="B9" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Ladubäcken-Rörmyran, Nb</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>790719</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7287498</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Piteå</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Norrfjärden</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22474-2024 artfynd.xlsx
+++ b/artfynd/A 22474-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119521076</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119521171</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119521207</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119521228</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119522576</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119522491</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,8 +1449,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119522629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>